--- a/SHOP.xlsx
+++ b/SHOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE9C9CF-640B-4423-BFF9-8569FCD31B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25792E7-2783-403F-80F2-4CEEABF0DBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{EB4D2DCC-174E-47B7-A437-CE6667273866}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{EB4D2DCC-174E-47B7-A437-CE6667273866}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>Shopify</t>
   </si>
@@ -175,18 +175,6 @@
     <t>Interest Income</t>
   </si>
   <si>
-    <t>Realzed gain on equity</t>
-  </si>
-  <si>
-    <t>Unrealized gain on equity</t>
-  </si>
-  <si>
-    <t>Net loss on equity method invest</t>
-  </si>
-  <si>
-    <t>Foreign exchange gain</t>
-  </si>
-  <si>
     <t>Pretax Income</t>
   </si>
   <si>
@@ -240,6 +228,30 @@
   <si>
     <t>Q425</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>FY23</t>
+  </si>
+  <si>
+    <t>FY22</t>
+  </si>
+  <si>
+    <t>FY21</t>
+  </si>
+  <si>
+    <t>FY20</t>
+  </si>
+  <si>
+    <t>Gains on Equity Investments</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
 </sst>
 </file>
 
@@ -248,13 +260,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -330,27 +348,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -707,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>150.69</v>
+        <v>122.04</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -715,11 +737,11 @@
         <v>3</v>
       </c>
       <c r="I3" s="3">
-        <f>1220.418767+79.241982</f>
-        <v>1299.6607489999999</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>53</v>
+        <f>1226.037779+78.073594</f>
+        <v>1304.111373</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -731,7 +753,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>195845.87826680997</v>
+        <v>159153.75196092</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -745,8 +767,8 @@
         <f>1542+4278</f>
         <v>5820</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>53</v>
+      <c r="J5" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -756,8 +778,8 @@
       <c r="I6" s="3">
         <v>919</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>53</v>
+      <c r="J6" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -766,7 +788,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>190944.87826680997</v>
+        <v>154252.75196092</v>
       </c>
     </row>
   </sheetData>
@@ -779,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{813D3D3C-6B04-4BB8-8C2B-9B579C85C635}">
-  <dimension ref="A1:BV253"/>
+  <dimension ref="A1:BV251"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -787,12 +809,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -818,19 +840,37 @@
         <v>18</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="W2" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>19</v>
@@ -847,8 +887,17 @@
       <c r="L3" s="10">
         <v>87837</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U3" s="10">
+        <v>235910</v>
+      </c>
+      <c r="V3" s="10">
+        <v>292275</v>
+      </c>
+      <c r="W3" s="10">
+        <v>378441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>20</v>
@@ -865,12 +914,21 @@
       <c r="L4" s="10">
         <v>185</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U4" s="10">
+        <v>144</v>
+      </c>
+      <c r="V4" s="10">
+        <v>178</v>
+      </c>
+      <c r="W4" s="10">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>21</v>
@@ -893,8 +951,17 @@
       <c r="L6" s="10">
         <v>656</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U6" s="10">
+        <v>1837</v>
+      </c>
+      <c r="V6" s="10">
+        <v>2350</v>
+      </c>
+      <c r="W6" s="10">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>22</v>
@@ -917,8 +984,17 @@
       <c r="L7" s="10">
         <v>2024</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="10">
+        <v>5223</v>
+      </c>
+      <c r="V7" s="10">
+        <v>6530</v>
+      </c>
+      <c r="W7" s="10">
+        <v>8804</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -971,8 +1047,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q8" s="11">
+        <f t="shared" ref="Q8:W8" si="2">+Q6+Q7</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="11">
+        <f t="shared" si="2"/>
+        <v>7060</v>
+      </c>
+      <c r="V8" s="11">
+        <f t="shared" si="2"/>
+        <v>8880</v>
+      </c>
+      <c r="W8" s="11">
+        <f t="shared" si="2"/>
+        <v>11556</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>23</v>
@@ -995,8 +1099,17 @@
       <c r="L9" s="10">
         <v>121</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U9" s="10">
+        <v>354</v>
+      </c>
+      <c r="V9" s="10">
+        <v>434</v>
+      </c>
+      <c r="W9" s="10">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -1019,34 +1132,43 @@
       <c r="L10" s="10">
         <v>1257</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U10" s="10">
+        <v>3191</v>
+      </c>
+      <c r="V10" s="10">
+        <v>3974</v>
+      </c>
+      <c r="W10" s="10">
+        <v>5481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="10">
-        <f t="shared" ref="C11:H11" si="2">+C8-C9-C10</f>
+        <f t="shared" ref="C11:H11" si="3">+C8-C9-C10</f>
         <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>901</v>
       </c>
       <c r="F11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>957</v>
       </c>
       <c r="H11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1045</v>
       </c>
       <c r="I11" s="10">
@@ -1054,27 +1176,55 @@
         <v>1118</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" ref="J11:N11" si="3">+J8-J9-J10</f>
+        <f t="shared" ref="J11:N11" si="4">+J8-J9-J10</f>
         <v>0</v>
       </c>
       <c r="K11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1169</v>
       </c>
       <c r="L11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1302</v>
       </c>
       <c r="M11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q11" s="10">
+        <f t="shared" ref="Q11:W11" si="5">+Q8-Q9-Q10</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="10">
+        <f t="shared" si="5"/>
+        <v>3515</v>
+      </c>
+      <c r="V11" s="10">
+        <f t="shared" si="5"/>
+        <v>4472</v>
+      </c>
+      <c r="W11" s="10">
+        <f t="shared" si="5"/>
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>26</v>
@@ -1097,8 +1247,17 @@
       <c r="L12" s="10">
         <v>415</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U12" s="10">
+        <v>1220</v>
+      </c>
+      <c r="V12" s="10">
+        <v>1393</v>
+      </c>
+      <c r="W12" s="10">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>27</v>
@@ -1121,8 +1280,17 @@
       <c r="L13" s="10">
         <v>394</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U13" s="10">
+        <v>1730</v>
+      </c>
+      <c r="V13" s="10">
+        <v>1367</v>
+      </c>
+      <c r="W13" s="10">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -1145,8 +1313,17 @@
       <c r="L14" s="10">
         <v>122</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U14" s="10">
+        <v>491</v>
+      </c>
+      <c r="V14" s="10">
+        <v>410</v>
+      </c>
+      <c r="W14" s="10">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1169,8 +1346,17 @@
       <c r="L15" s="10">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U15" s="10">
+        <v>152</v>
+      </c>
+      <c r="V15" s="10">
+        <v>227</v>
+      </c>
+      <c r="W15" s="10">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>30</v>
@@ -1191,6 +1377,15 @@
         <v>0</v>
       </c>
       <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="U16" s="10">
+        <v>1340</v>
+      </c>
+      <c r="V16" s="10">
+        <v>0</v>
+      </c>
+      <c r="W16" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1200,27 +1395,27 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <f t="shared" ref="C17:H17" si="4">+C11-SUM(C12:C16)</f>
+        <f t="shared" ref="C17:H17" si="6">+C11-SUM(C12:C16)</f>
         <v>0</v>
       </c>
       <c r="D17" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>122</v>
       </c>
       <c r="F17" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>241</v>
       </c>
       <c r="I17" s="10">
@@ -1228,24 +1423,52 @@
         <v>283</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" ref="J17:N17" si="5">+J11-SUM(J12:J16)</f>
+        <f t="shared" ref="J17:N17" si="7">+J11-SUM(J12:J16)</f>
         <v>0</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>203</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>291</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <f t="shared" ref="Q17:W17" si="8">+Q11-SUM(Q12:Q16)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="10">
+        <f t="shared" si="8"/>
+        <v>-1418</v>
+      </c>
+      <c r="V17" s="10">
+        <f t="shared" si="8"/>
+        <v>1075</v>
+      </c>
+      <c r="W17" s="10">
+        <f t="shared" si="8"/>
+        <v>1468</v>
       </c>
     </row>
     <row r="18" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -1271,291 +1494,519 @@
       <c r="L18" s="10">
         <v>106</v>
       </c>
+      <c r="U18" s="10">
+        <v>1361</v>
+      </c>
+      <c r="V18" s="10">
+        <v>853</v>
+      </c>
+      <c r="W18" s="10">
+        <v>357</v>
+      </c>
     </row>
     <row r="19" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>34</v>
+      <c r="B19" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="E19" s="10">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="G19" s="10">
-        <v>-373</v>
+        <f>-373-44</f>
+        <v>-417</v>
       </c>
       <c r="H19" s="10">
-        <v>3</v>
+        <f>3-79</f>
+        <v>-76</v>
       </c>
       <c r="I19" s="10">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="K19" s="10">
-        <v>-1021</v>
+        <f>-1021-23</f>
+        <v>-1044</v>
       </c>
       <c r="L19" s="10">
-        <v>1</v>
+        <f>1+681</f>
+        <v>682</v>
+      </c>
+      <c r="U19" s="10">
+        <v>242</v>
+      </c>
+      <c r="V19" s="10">
+        <v>300</v>
+      </c>
+      <c r="W19" s="10">
+        <v>-316</v>
       </c>
     </row>
     <row r="20" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>35</v>
+      <c r="B20" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="E20" s="10">
-        <v>555</v>
+        <v>-12</v>
       </c>
       <c r="G20" s="10">
-        <v>-44</v>
+        <v>-4</v>
       </c>
       <c r="H20" s="10">
-        <v>-79</v>
+        <f>-44+2</f>
+        <v>-42</v>
       </c>
       <c r="I20" s="10">
-        <v>512</v>
+        <f>-28+16</f>
+        <v>-12</v>
       </c>
       <c r="K20" s="10">
-        <v>-23</v>
+        <v>-6</v>
       </c>
       <c r="L20" s="10">
-        <v>681</v>
+        <v>0</v>
+      </c>
+      <c r="U20" s="10">
+        <v>0</v>
+      </c>
+      <c r="V20" s="10">
+        <v>0</v>
+      </c>
+      <c r="W20" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="C21" s="10">
+        <f>+C17+C18+C19+C20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" ref="D21:N21" si="9">+D17+D18+D19+D20</f>
+        <v>0</v>
       </c>
       <c r="E21" s="10">
-        <v>10</v>
+        <f t="shared" si="9"/>
+        <v>728</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="G21" s="10">
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>-256</v>
       </c>
       <c r="H21" s="10">
-        <v>44</v>
+        <f t="shared" si="9"/>
+        <v>203</v>
       </c>
       <c r="I21" s="10">
-        <v>28</v>
+        <f t="shared" si="9"/>
+        <v>860</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="K21" s="10">
-        <v>-6</v>
+        <f t="shared" si="9"/>
+        <v>-782</v>
       </c>
       <c r="L21" s="10">
-        <v>24</v>
+        <f t="shared" si="9"/>
+        <v>1079</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10">
+        <f t="shared" ref="Q21" si="10">+Q17+Q18+Q19+Q20</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
+        <f t="shared" ref="R21" si="11">+R17+R18+R19+R20</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" ref="S21" si="12">+S17+S18+S19+S20</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="10">
+        <f t="shared" ref="T21" si="13">+T17+T18+T19+T20</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="10">
+        <f t="shared" ref="U21" si="14">+U17+U18+U19+U20</f>
+        <v>185</v>
+      </c>
+      <c r="V21" s="10">
+        <f t="shared" ref="V21" si="15">+V17+V18+V19+V20</f>
+        <v>2228</v>
+      </c>
+      <c r="W21" s="10">
+        <f t="shared" ref="W21" si="16">+W17+W18+W19+W20</f>
+        <v>1509</v>
       </c>
     </row>
     <row r="22" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E22" s="10">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="G22" s="10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H22" s="10">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I22" s="10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K22" s="10">
-        <v>0</v>
+        <v>-88</v>
       </c>
       <c r="L22" s="10">
-        <v>24</v>
+        <v>173</v>
+      </c>
+      <c r="U22" s="10">
+        <v>53</v>
+      </c>
+      <c r="V22" s="10">
+        <v>209</v>
+      </c>
+      <c r="W22" s="10">
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:H23" si="6">+C17+C18+C19+C20-C21+C22</f>
+        <f t="shared" ref="C23:H23" si="17">+C21-C22</f>
         <v>0</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="6"/>
-        <v>728</v>
+        <f t="shared" si="17"/>
+        <v>718</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="6"/>
-        <v>-256</v>
+        <f t="shared" si="17"/>
+        <v>-273</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="6"/>
-        <v>203</v>
+        <f t="shared" si="17"/>
+        <v>171</v>
       </c>
       <c r="I23" s="10">
-        <f>+I17+I18+I19+I20-I21+I22</f>
-        <v>860</v>
+        <f>+I21-I22</f>
+        <v>828</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" ref="J23:N23" si="7">+J17+J18+J19+J20-J21+J22</f>
+        <f t="shared" ref="J23:N23" si="18">+J21-J22</f>
         <v>0</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="7"/>
-        <v>-770</v>
+        <f t="shared" si="18"/>
+        <v>-694</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="7"/>
-        <v>1079</v>
+        <f t="shared" si="18"/>
+        <v>906</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0</v>
+      </c>
+      <c r="T23" s="10">
+        <f>+T21-T22</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="10">
+        <f>+U21-U22</f>
+        <v>132</v>
+      </c>
+      <c r="V23" s="10">
+        <f>+V21-V22</f>
+        <v>2019</v>
+      </c>
+      <c r="W23" s="10">
+        <f>+W21-W22</f>
+        <v>1231</v>
       </c>
     </row>
     <row r="24" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="10">
-        <v>10</v>
-      </c>
-      <c r="G24" s="10">
-        <v>17</v>
-      </c>
-      <c r="H24" s="10">
-        <v>32</v>
-      </c>
-      <c r="I24" s="10">
-        <v>32</v>
-      </c>
-      <c r="K24" s="10">
-        <v>-88</v>
-      </c>
-      <c r="L24" s="10">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:74" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="10">
-        <f t="shared" ref="C25:H25" si="8">+C23-C24</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="10">
-        <f t="shared" si="8"/>
-        <v>718</v>
-      </c>
-      <c r="F25" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="10">
-        <f t="shared" si="8"/>
-        <v>-273</v>
-      </c>
-      <c r="H25" s="10">
-        <f t="shared" si="8"/>
-        <v>171</v>
-      </c>
-      <c r="I25" s="10">
-        <f>+I23-I24</f>
-        <v>828</v>
-      </c>
-      <c r="J25" s="10">
-        <f t="shared" ref="J25:N25" si="9">+J23-J24</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="10">
-        <f t="shared" si="9"/>
-        <v>-682</v>
-      </c>
-      <c r="L25" s="10">
-        <f t="shared" si="9"/>
-        <v>906</v>
-      </c>
-      <c r="M25" s="10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:74" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="C25" s="7" t="e">
+        <f t="shared" ref="C25:D25" si="19">+C23/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D25" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E25" s="7">
+        <f>+E23/E26</f>
+        <v>0.55948231578205332</v>
+      </c>
+      <c r="F25" s="7" t="e">
+        <f t="shared" ref="F25:N25" si="20">+F23/F26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="7">
+        <f t="shared" si="20"/>
+        <v>-0.21205914008764981</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="20"/>
+        <v>0.13267125123839013</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="20"/>
+        <v>0.64156930902766907</v>
+      </c>
+      <c r="J25" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="20"/>
+        <v>-0.53575121262577929</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="20"/>
+        <v>0.69813350616632586</v>
+      </c>
+      <c r="M25" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="7" t="e">
+        <f t="shared" ref="Q25:W25" si="21">+Q23/Q26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R25" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="7">
+        <f t="shared" si="21"/>
+        <v>0.10299990669378907</v>
+      </c>
+      <c r="V25" s="7">
+        <f t="shared" si="21"/>
+        <v>1.5653442562926319</v>
+      </c>
+      <c r="W25" s="7">
+        <f t="shared" si="21"/>
+        <v>0.94768424232675619</v>
+      </c>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="3"/>
+      <c r="BC25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="3"/>
+      <c r="BF25" s="3"/>
+      <c r="BG25" s="3"/>
+      <c r="BH25" s="3"/>
+      <c r="BI25" s="3"/>
+      <c r="BJ25" s="3"/>
+      <c r="BK25" s="3"/>
+      <c r="BL25" s="3"/>
+      <c r="BM25" s="3"/>
+      <c r="BN25" s="3"/>
+      <c r="BO25" s="3"/>
+      <c r="BP25" s="3"/>
+      <c r="BQ25" s="3"/>
+      <c r="BR25" s="3"/>
+      <c r="BS25" s="3"/>
+      <c r="BT25" s="3"/>
+      <c r="BU25" s="3"/>
+      <c r="BV25" s="3"/>
+    </row>
+    <row r="26" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
+        <v>1283.329213</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3">
+        <v>1287.3767190000001</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1288.900183</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1290.5854260000001</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3">
+        <v>1295.3773759999999</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1297.74605</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3">
+        <v>1281.5545589999999</v>
+      </c>
+      <c r="V26" s="3">
+        <v>1289.812124</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1298.95586</v>
+      </c>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="3"/>
+      <c r="AU26" s="3"/>
+      <c r="AV26" s="3"/>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="3"/>
+      <c r="BC26" s="3"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="3"/>
+      <c r="BF26" s="3"/>
+      <c r="BG26" s="3"/>
+      <c r="BH26" s="3"/>
+      <c r="BI26" s="3"/>
+      <c r="BJ26" s="3"/>
+      <c r="BK26" s="3"/>
+      <c r="BL26" s="3"/>
+      <c r="BM26" s="3"/>
+      <c r="BN26" s="3"/>
+      <c r="BO26" s="3"/>
+      <c r="BP26" s="3"/>
+      <c r="BQ26" s="3"/>
+      <c r="BR26" s="3"/>
+      <c r="BS26" s="3"/>
+      <c r="BT26" s="3"/>
+      <c r="BU26" s="3"/>
+      <c r="BV26" s="3"/>
     </row>
     <row r="27" spans="1:74" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="7" t="e">
-        <f t="shared" ref="C27:D27" si="10">+C25/C28</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D27" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E27" s="7">
-        <f>+E25/E28</f>
-        <v>0.55948231578205332</v>
-      </c>
-      <c r="F27" s="7" t="e">
-        <f t="shared" ref="F27:N27" si="11">+F25/F28</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G27" s="7">
-        <f t="shared" si="11"/>
-        <v>-0.21205914008764981</v>
-      </c>
-      <c r="H27" s="7">
-        <f t="shared" si="11"/>
-        <v>0.13267125123839013</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" si="11"/>
-        <v>0.64156930902766907</v>
-      </c>
-      <c r="J27" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="7">
-        <f t="shared" si="11"/>
-        <v>-0.52648750289737967</v>
-      </c>
-      <c r="L27" s="7">
-        <f t="shared" si="11"/>
-        <v>0.69813350616632586</v>
-      </c>
-      <c r="M27" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
@@ -1619,32 +2070,44 @@
     </row>
     <row r="28" spans="1:74" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3">
-        <v>1283.329213</v>
-      </c>
+      <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3">
-        <v>1287.3767190000001</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1288.900183</v>
-      </c>
-      <c r="I28" s="3">
-        <v>1290.5854260000001</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3">
-        <v>1295.3773759999999</v>
-      </c>
-      <c r="L28" s="3">
-        <v>1297.74605</v>
-      </c>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="G28" s="8" t="e">
+        <f>+G3/C3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H28" s="8" t="e">
+        <f>+H3/D3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I28" s="8">
+        <f>+I3/E3-1</f>
+        <v>0.24037007383684728</v>
+      </c>
+      <c r="J28" s="8" t="e">
+        <f>+J3/F3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="8" t="e">
+        <f>+K3/G3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="8">
+        <f>+L3/H3-1</f>
+        <v>0.30622351104171308</v>
+      </c>
+      <c r="M28" s="8">
+        <f>+M3/I3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="N28" s="8" t="e">
+        <f>+N3/J3-1</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -1652,8 +2115,14 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
+      <c r="V28" s="8">
+        <f>+V3/U3-1</f>
+        <v>0.2389258615573735</v>
+      </c>
+      <c r="W28" s="8">
+        <f t="shared" ref="W28:W29" si="22">+W3/V3-1</f>
+        <v>0.29481139337952267</v>
+      </c>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
@@ -1707,18 +2176,45 @@
       <c r="BV28" s="3"/>
     </row>
     <row r="29" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="G29" s="8" t="e">
+        <f>+G4/C4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H29" s="8" t="e">
+        <f>+H4/D4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="8">
+        <f>+I4/E4-1</f>
+        <v>0.27737226277372273</v>
+      </c>
+      <c r="J29" s="8" t="e">
+        <f>+J4/F4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="8" t="e">
+        <f>+K4/G4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L29" s="8">
+        <f>+L4/H4-1</f>
+        <v>9.4674556213017791E-2</v>
+      </c>
+      <c r="M29" s="8">
+        <f>+M4/I4-1</f>
+        <v>-1</v>
+      </c>
+      <c r="N29" s="8" t="e">
+        <f>+N4/J4-1</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
@@ -1726,8 +2222,14 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
+      <c r="V29" s="8">
+        <f>+V4/U4-1</f>
+        <v>0.23611111111111116</v>
+      </c>
+      <c r="W29" s="8">
+        <f t="shared" si="22"/>
+        <v>0.151685393258427</v>
+      </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
@@ -1782,42 +2284,42 @@
     </row>
     <row r="30" spans="1:74" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="8" t="e">
-        <f t="shared" ref="G30:H31" si="12">+G3/C3-1</f>
+        <f>+G6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f>+H6/D6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I30" s="8">
-        <f>+I3/E3-1</f>
-        <v>0.24037007383684728</v>
+        <f>+I6/E6-1</f>
+        <v>0.25514403292181065</v>
       </c>
       <c r="J30" s="8" t="e">
-        <f t="shared" ref="J30:N31" si="13">+J3/F3-1</f>
+        <f>+J6/F6-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K30" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+      <c r="K30" s="8">
+        <f>+K6/G6-1</f>
+        <v>0.21330724070450091</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="13"/>
-        <v>0.30622351104171308</v>
+        <f>+L6/H6-1</f>
+        <v>0.1651865008880995</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="13"/>
+        <f>+M6/I6-1</f>
         <v>-1</v>
       </c>
       <c r="N30" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+N6/J6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O30" s="3"/>
@@ -1826,9 +2328,18 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
+      <c r="U30" s="8" t="e">
+        <f t="shared" ref="U30:W30" si="23">+U6/T6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" s="8">
+        <f t="shared" si="23"/>
+        <v>0.27925966249319534</v>
+      </c>
+      <c r="W30" s="8">
+        <f>+W6/V6-1</f>
+        <v>0.171063829787234</v>
+      </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
@@ -1883,42 +2394,42 @@
     </row>
     <row r="31" spans="1:74" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f>+G7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f>+H7/D7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" ref="I31:J31" si="14">+I4/E4-1</f>
-        <v>0.27737226277372273</v>
+        <f>+I7/E7-1</f>
+        <v>0.26384364820846895</v>
       </c>
       <c r="J31" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+J7/F7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K31" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+      <c r="K31" s="8">
+        <f>+K7/G7-1</f>
+        <v>0.28888888888888897</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="13"/>
-        <v>9.4674556213017791E-2</v>
+        <f>+L7/H7-1</f>
+        <v>0.36572199730094468</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="13"/>
+        <f>+M7/I7-1</f>
         <v>-1</v>
       </c>
       <c r="N31" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+N7/J7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O31" s="3"/>
@@ -1927,9 +2438,18 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
+      <c r="U31" s="8" t="e">
+        <f t="shared" ref="U31:W32" si="24">+U7/T7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" s="8">
+        <f t="shared" si="24"/>
+        <v>0.25023932605782107</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" si="24"/>
+        <v>0.34823889739663083</v>
+      </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -1982,156 +2502,198 @@
       <c r="BU31" s="3"/>
       <c r="BV31" s="3"/>
     </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="8" t="e">
-        <f t="shared" ref="G32:H34" si="15">+G6/C6-1</f>
+    <row r="32" spans="1:74" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="12" t="e">
+        <f>+G8/C8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="8" t="e">
-        <f t="shared" si="15"/>
+      <c r="H32" s="12" t="e">
+        <f>+H8/D8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I32" s="8">
-        <f>+I6/E6-1</f>
-        <v>0.25514403292181065</v>
-      </c>
-      <c r="J32" s="8" t="e">
-        <f t="shared" ref="J32:N34" si="16">+J6/F6-1</f>
+      <c r="I32" s="12">
+        <f>+I8/E8-1</f>
+        <v>0.26137689614935833</v>
+      </c>
+      <c r="J32" s="12" t="e">
+        <f>+J8/F8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K32" s="8">
-        <f t="shared" si="16"/>
-        <v>0.21330724070450091</v>
-      </c>
-      <c r="L32" s="8">
-        <f t="shared" si="16"/>
-        <v>0.1651865008880995</v>
-      </c>
-      <c r="M32" s="8">
-        <f t="shared" si="16"/>
+      <c r="K32" s="12">
+        <f>+K8/G8-1</f>
+        <v>0.26813541106931749</v>
+      </c>
+      <c r="L32" s="12">
+        <f>+L8/H8-1</f>
+        <v>0.31051344743276288</v>
+      </c>
+      <c r="M32" s="12">
+        <f>+M8/I8-1</f>
         <v>-1</v>
       </c>
-      <c r="N32" s="8" t="e">
-        <f t="shared" si="16"/>
+      <c r="N32" s="12" t="e">
+        <f>+N8/J8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
-      <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
-      <c r="AE32" s="3"/>
-      <c r="AF32" s="3"/>
-      <c r="AG32" s="3"/>
-      <c r="AH32" s="3"/>
-      <c r="AI32" s="3"/>
-      <c r="AJ32" s="3"/>
-      <c r="AK32" s="3"/>
-      <c r="AL32" s="3"/>
-      <c r="AM32" s="3"/>
-      <c r="AN32" s="3"/>
-      <c r="AO32" s="3"/>
-      <c r="AP32" s="3"/>
-      <c r="AQ32" s="3"/>
-      <c r="AR32" s="3"/>
-      <c r="AS32" s="3"/>
-      <c r="AT32" s="3"/>
-      <c r="AU32" s="3"/>
-      <c r="AV32" s="3"/>
-      <c r="AW32" s="3"/>
-      <c r="AX32" s="3"/>
-      <c r="AY32" s="3"/>
-      <c r="AZ32" s="3"/>
-      <c r="BA32" s="3"/>
-      <c r="BB32" s="3"/>
-      <c r="BC32" s="3"/>
-      <c r="BD32" s="3"/>
-      <c r="BE32" s="3"/>
-      <c r="BF32" s="3"/>
-      <c r="BG32" s="3"/>
-      <c r="BH32" s="3"/>
-      <c r="BI32" s="3"/>
-      <c r="BJ32" s="3"/>
-      <c r="BK32" s="3"/>
-      <c r="BL32" s="3"/>
-      <c r="BM32" s="3"/>
-      <c r="BN32" s="3"/>
-      <c r="BO32" s="3"/>
-      <c r="BP32" s="3"/>
-      <c r="BQ32" s="3"/>
-      <c r="BR32" s="3"/>
-      <c r="BS32" s="3"/>
-      <c r="BT32" s="3"/>
-      <c r="BU32" s="3"/>
-      <c r="BV32" s="3"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="12" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V32" s="12">
+        <f t="shared" si="24"/>
+        <v>0.25779036827195467</v>
+      </c>
+      <c r="W32" s="12">
+        <f t="shared" si="24"/>
+        <v>0.30135135135135127</v>
+      </c>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="6"/>
+      <c r="AL32" s="6"/>
+      <c r="AM32" s="6"/>
+      <c r="AN32" s="6"/>
+      <c r="AO32" s="6"/>
+      <c r="AP32" s="6"/>
+      <c r="AQ32" s="6"/>
+      <c r="AR32" s="6"/>
+      <c r="AS32" s="6"/>
+      <c r="AT32" s="6"/>
+      <c r="AU32" s="6"/>
+      <c r="AV32" s="6"/>
+      <c r="AW32" s="6"/>
+      <c r="AX32" s="6"/>
+      <c r="AY32" s="6"/>
+      <c r="AZ32" s="6"/>
+      <c r="BA32" s="6"/>
+      <c r="BB32" s="6"/>
+      <c r="BC32" s="6"/>
+      <c r="BD32" s="6"/>
+      <c r="BE32" s="6"/>
+      <c r="BF32" s="6"/>
+      <c r="BG32" s="6"/>
+      <c r="BH32" s="6"/>
+      <c r="BI32" s="6"/>
+      <c r="BJ32" s="6"/>
+      <c r="BK32" s="6"/>
+      <c r="BL32" s="6"/>
+      <c r="BM32" s="6"/>
+      <c r="BN32" s="6"/>
+      <c r="BO32" s="6"/>
+      <c r="BP32" s="6"/>
+      <c r="BQ32" s="6"/>
+      <c r="BR32" s="6"/>
+      <c r="BS32" s="6"/>
+      <c r="BT32" s="6"/>
+      <c r="BU32" s="6"/>
+      <c r="BV32" s="6"/>
     </row>
     <row r="33" spans="2:74" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="8" t="e">
-        <f t="shared" si="15"/>
+        <v>43</v>
+      </c>
+      <c r="C33" s="8" t="e">
+        <f>+(C6-C9)/C6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="8" t="e">
-        <f t="shared" si="15"/>
+      <c r="D33" s="8" t="e">
+        <f>+(D6-D9)/D6</f>
         <v>#DIV/0!</v>
       </c>
+      <c r="E33" s="8">
+        <f>+(E6-E9)/E6</f>
+        <v>0.81893004115226342</v>
+      </c>
+      <c r="F33" s="8" t="e">
+        <f>+(F6-F9)/F6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="8">
+        <f>+(G6-G9)/G6</f>
+        <v>0.81409001956947158</v>
+      </c>
+      <c r="H33" s="8">
+        <f>+(H6-H9)/H6</f>
+        <v>0.82770870337477798</v>
+      </c>
       <c r="I33" s="8">
-        <f t="shared" ref="I33:J34" si="17">+I7/E7-1</f>
-        <v>0.26384364820846895</v>
+        <f>+(I6-I9)/I6</f>
+        <v>0.82295081967213113</v>
       </c>
       <c r="J33" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f>+(J6-J9)/J6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="16"/>
-        <v>0.28888888888888897</v>
+        <f>+(K6-K9)/K6</f>
+        <v>0.80161290322580647</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="16"/>
-        <v>0.36572199730094468</v>
-      </c>
-      <c r="M33" s="8">
-        <f t="shared" si="16"/>
-        <v>-1</v>
+        <f>+(L6-L9)/L6</f>
+        <v>0.81554878048780488</v>
+      </c>
+      <c r="M33" s="8" t="e">
+        <f>+(M6-M9)/M6</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N33" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f>+(N6-N9)/N6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
+      <c r="Q33" s="8" t="e">
+        <f t="shared" ref="Q33:W33" si="25">+(Q6-Q9)/Q6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" s="8" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S33" s="8" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T33" s="8" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="8">
+        <f t="shared" si="25"/>
+        <v>0.8072945019052804</v>
+      </c>
+      <c r="V33" s="8">
+        <f t="shared" si="25"/>
+        <v>0.81531914893617019</v>
+      </c>
+      <c r="W33" s="8">
+        <f t="shared" si="25"/>
+        <v>0.81104651162790697</v>
+      </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
@@ -2184,168 +2746,222 @@
       <c r="BU33" s="3"/>
       <c r="BV33" s="3"/>
     </row>
-    <row r="34" spans="2:74" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="12" t="e">
-        <f t="shared" si="15"/>
+    <row r="34" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="8" t="e">
+        <f>+(C7-C10)/C7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="12" t="e">
-        <f t="shared" si="15"/>
+      <c r="D34" s="8" t="e">
+        <f>+(D7-D10)/D7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I34" s="12">
-        <f t="shared" si="17"/>
-        <v>0.26137689614935833</v>
-      </c>
-      <c r="J34" s="12" t="e">
-        <f t="shared" si="16"/>
+      <c r="E34" s="8">
+        <f>+(E7-E10)/E7</f>
+        <v>0.40960912052117265</v>
+      </c>
+      <c r="F34" s="8" t="e">
+        <f>+(F7-F10)/F7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K34" s="12">
-        <f t="shared" si="16"/>
-        <v>0.26813541106931749</v>
-      </c>
-      <c r="L34" s="12">
-        <f t="shared" si="16"/>
-        <v>0.31051344743276288</v>
-      </c>
-      <c r="M34" s="12">
-        <f t="shared" si="16"/>
-        <v>-1</v>
-      </c>
-      <c r="N34" s="12" t="e">
-        <f t="shared" si="16"/>
+      <c r="G34" s="8">
+        <f>+(G7-G10)/G7</f>
+        <v>0.40074074074074073</v>
+      </c>
+      <c r="H34" s="8">
+        <f>+(H7-H10)/H7</f>
+        <v>0.39068825910931176</v>
+      </c>
+      <c r="I34" s="8">
+        <f>+(I7-I10)/I7</f>
+        <v>0.39690721649484534</v>
+      </c>
+      <c r="J34" s="8" t="e">
+        <f>+(J7-J10)/J7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="6"/>
-      <c r="AB34" s="6"/>
-      <c r="AC34" s="6"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="6"/>
-      <c r="AO34" s="6"/>
-      <c r="AP34" s="6"/>
-      <c r="AQ34" s="6"/>
-      <c r="AR34" s="6"/>
-      <c r="AS34" s="6"/>
-      <c r="AT34" s="6"/>
-      <c r="AU34" s="6"/>
-      <c r="AV34" s="6"/>
-      <c r="AW34" s="6"/>
-      <c r="AX34" s="6"/>
-      <c r="AY34" s="6"/>
-      <c r="AZ34" s="6"/>
-      <c r="BA34" s="6"/>
-      <c r="BB34" s="6"/>
-      <c r="BC34" s="6"/>
-      <c r="BD34" s="6"/>
-      <c r="BE34" s="6"/>
-      <c r="BF34" s="6"/>
-      <c r="BG34" s="6"/>
-      <c r="BH34" s="6"/>
-      <c r="BI34" s="6"/>
-      <c r="BJ34" s="6"/>
-      <c r="BK34" s="6"/>
-      <c r="BL34" s="6"/>
-      <c r="BM34" s="6"/>
-      <c r="BN34" s="6"/>
-      <c r="BO34" s="6"/>
-      <c r="BP34" s="6"/>
-      <c r="BQ34" s="6"/>
-      <c r="BR34" s="6"/>
-      <c r="BS34" s="6"/>
-      <c r="BT34" s="6"/>
-      <c r="BU34" s="6"/>
-      <c r="BV34" s="6"/>
+      <c r="K34" s="8">
+        <f>+(K7-K10)/K7</f>
+        <v>0.38620689655172413</v>
+      </c>
+      <c r="L34" s="8">
+        <f>+(L7-L10)/L7</f>
+        <v>0.37895256916996045</v>
+      </c>
+      <c r="M34" s="8" t="e">
+        <f>+(M7-M10)/M7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="8" t="e">
+        <f>+(N7-N10)/N7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="8" t="e">
+        <f t="shared" ref="Q34:W34" si="26">+(Q7-Q10)/Q7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R34" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S34" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T34" s="8" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="8">
+        <f t="shared" si="26"/>
+        <v>0.38904843959410301</v>
+      </c>
+      <c r="V34" s="8">
+        <f t="shared" si="26"/>
+        <v>0.39142419601837675</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" si="26"/>
+        <v>0.377442071785552</v>
+      </c>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="3"/>
+      <c r="AK34" s="3"/>
+      <c r="AL34" s="3"/>
+      <c r="AM34" s="3"/>
+      <c r="AN34" s="3"/>
+      <c r="AO34" s="3"/>
+      <c r="AP34" s="3"/>
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="3"/>
+      <c r="AT34" s="3"/>
+      <c r="AU34" s="3"/>
+      <c r="AV34" s="3"/>
+      <c r="AW34" s="3"/>
+      <c r="AX34" s="3"/>
+      <c r="AY34" s="3"/>
+      <c r="AZ34" s="3"/>
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="3"/>
+      <c r="BC34" s="3"/>
+      <c r="BD34" s="3"/>
+      <c r="BE34" s="3"/>
+      <c r="BF34" s="3"/>
+      <c r="BG34" s="3"/>
+      <c r="BH34" s="3"/>
+      <c r="BI34" s="3"/>
+      <c r="BJ34" s="3"/>
+      <c r="BK34" s="3"/>
+      <c r="BL34" s="3"/>
+      <c r="BM34" s="3"/>
+      <c r="BN34" s="3"/>
+      <c r="BO34" s="3"/>
+      <c r="BP34" s="3"/>
+      <c r="BQ34" s="3"/>
+      <c r="BR34" s="3"/>
+      <c r="BS34" s="3"/>
+      <c r="BT34" s="3"/>
+      <c r="BU34" s="3"/>
+      <c r="BV34" s="3"/>
     </row>
     <row r="35" spans="2:74" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C35" s="8" t="e">
-        <f t="shared" ref="C35:H35" si="18">+(C6-C9)/C6</f>
+        <f>+C11/C8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f>+D11/D8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E35" s="8">
-        <f t="shared" si="18"/>
-        <v>0.81893004115226342</v>
+        <f>+E11/E8</f>
+        <v>0.52567094515752621</v>
       </c>
       <c r="F35" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f>+F11/F8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="8">
-        <f t="shared" si="18"/>
-        <v>0.81409001956947158</v>
+        <f>+G11/G8</f>
+        <v>0.51423965609887157</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" si="18"/>
-        <v>0.82770870337477798</v>
+        <f>+H11/H8</f>
+        <v>0.51100244498777503</v>
       </c>
       <c r="I35" s="8">
-        <f>+(I6-I9)/I6</f>
-        <v>0.82295081967213113</v>
+        <f>+I11/I8</f>
+        <v>0.51711378353376503</v>
       </c>
       <c r="J35" s="8" t="e">
-        <f t="shared" ref="J35:N35" si="19">+(J6-J9)/J6</f>
+        <f>+J11/J8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="19"/>
-        <v>0.80161290322580647</v>
+        <f>+K11/K8</f>
+        <v>0.49533898305084745</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" si="19"/>
-        <v>0.81554878048780488</v>
+        <f>+L11/L8</f>
+        <v>0.48582089552238805</v>
       </c>
       <c r="M35" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f>+M11/M8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N35" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f>+N11/N8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
+      <c r="Q35" s="8" t="e">
+        <f t="shared" ref="Q35:W35" si="27">+Q11/Q8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R35" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S35" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T35" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" s="8">
+        <f t="shared" si="27"/>
+        <v>0.49787535410764872</v>
+      </c>
+      <c r="V35" s="8">
+        <f t="shared" si="27"/>
+        <v>0.50360360360360357</v>
+      </c>
+      <c r="W35" s="8">
+        <f t="shared" si="27"/>
+        <v>0.48070266528210454</v>
+      </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
@@ -2400,65 +3016,86 @@
     </row>
     <row r="36" spans="2:74" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C36" s="8" t="e">
-        <f t="shared" ref="C36:H36" si="20">+(C7-C10)/C7</f>
+        <f>+C17/C8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D36" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f>+D17/D8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="20"/>
-        <v>0.40960912052117265</v>
+        <f>+E17/E8</f>
+        <v>7.1178529754959155E-2</v>
       </c>
       <c r="F36" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f>+F17/F8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="8">
-        <f t="shared" si="20"/>
-        <v>0.40074074074074073</v>
+        <f>+G17/G8</f>
+        <v>4.6211714132186998E-2</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" si="20"/>
-        <v>0.39068825910931176</v>
+        <f>+H17/H8</f>
+        <v>0.11784841075794621</v>
       </c>
       <c r="I36" s="8">
-        <f>+(I7-I10)/I7</f>
-        <v>0.39690721649484534</v>
+        <f>+I17/I8</f>
+        <v>0.13089731729879742</v>
       </c>
       <c r="J36" s="8" t="e">
-        <f t="shared" ref="J36:N36" si="21">+(J7-J10)/J7</f>
+        <f>+J17/J8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="21"/>
-        <v>0.38620689655172413</v>
+        <f>+K17/K8</f>
+        <v>8.6016949152542377E-2</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" si="21"/>
-        <v>0.37895256916996045</v>
+        <f>+L17/L8</f>
+        <v>0.1085820895522388</v>
       </c>
       <c r="M36" s="8" t="e">
-        <f t="shared" si="21"/>
+        <f>+M17/M8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="8" t="e">
-        <f t="shared" si="21"/>
+        <f>+N17/N8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
+      <c r="Q36" s="8" t="e">
+        <f t="shared" ref="Q36:W36" si="28">+Q17/Q8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R36" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S36" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U36" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.2008498583569405</v>
+      </c>
+      <c r="V36" s="8">
+        <f t="shared" si="28"/>
+        <v>0.12105855855855856</v>
+      </c>
+      <c r="W36" s="8">
+        <f t="shared" si="28"/>
+        <v>0.12703357563170647</v>
+      </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
@@ -2513,65 +3150,86 @@
     </row>
     <row r="37" spans="2:74" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C37" s="8" t="e">
-        <f t="shared" ref="C37:H37" si="22">+C11/C8</f>
+        <f t="shared" ref="C37:H37" si="29">+C22/C21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D37" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E37" s="8">
-        <f t="shared" si="22"/>
-        <v>0.52567094515752621</v>
+        <f t="shared" si="29"/>
+        <v>1.3736263736263736E-2</v>
       </c>
       <c r="F37" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" si="22"/>
-        <v>0.51423965609887157</v>
+        <f t="shared" si="29"/>
+        <v>-6.640625E-2</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" si="22"/>
-        <v>0.51100244498777503</v>
+        <f t="shared" si="29"/>
+        <v>0.15763546798029557</v>
       </c>
       <c r="I37" s="8">
-        <f>+I11/I8</f>
-        <v>0.51711378353376503</v>
+        <f>+I22/I21</f>
+        <v>3.7209302325581395E-2</v>
       </c>
       <c r="J37" s="8" t="e">
-        <f t="shared" ref="J37:N37" si="23">+J11/J8</f>
+        <f t="shared" ref="J37:N37" si="30">+J22/J21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" si="23"/>
-        <v>0.49533898305084745</v>
+        <f t="shared" si="30"/>
+        <v>0.11253196930946291</v>
       </c>
       <c r="L37" s="8">
-        <f t="shared" si="23"/>
-        <v>0.48582089552238805</v>
+        <f t="shared" si="30"/>
+        <v>0.1603336422613531</v>
       </c>
       <c r="M37" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N37" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
+      <c r="Q37" s="8" t="e">
+        <f t="shared" ref="Q37:W37" si="31">+Q22/Q21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R37" s="8" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S37" s="8" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T37" s="8" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U37" s="8">
+        <f t="shared" si="31"/>
+        <v>0.2864864864864865</v>
+      </c>
+      <c r="V37" s="8">
+        <f t="shared" si="31"/>
+        <v>9.380610412926392E-2</v>
+      </c>
+      <c r="W37" s="8">
+        <f t="shared" si="31"/>
+        <v>0.18422796554009277</v>
+      </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
@@ -2625,57 +3283,18 @@
       <c r="BV37" s="3"/>
     </row>
     <row r="38" spans="2:74" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="8" t="e">
-        <f t="shared" ref="C38:H38" si="24">+C17/C8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D38" s="8" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="8">
-        <f t="shared" si="24"/>
-        <v>7.1178529754959155E-2</v>
-      </c>
-      <c r="F38" s="8" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G38" s="8">
-        <f t="shared" si="24"/>
-        <v>4.6211714132186998E-2</v>
-      </c>
-      <c r="H38" s="8">
-        <f t="shared" si="24"/>
-        <v>0.11784841075794621</v>
-      </c>
-      <c r="I38" s="8">
-        <f>+I17/I8</f>
-        <v>0.13089731729879742</v>
-      </c>
-      <c r="J38" s="8" t="e">
-        <f t="shared" ref="J38:N38" si="25">+J17/J8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K38" s="8">
-        <f t="shared" si="25"/>
-        <v>8.6016949152542377E-2</v>
-      </c>
-      <c r="L38" s="8">
-        <f t="shared" si="25"/>
-        <v>0.1085820895522388</v>
-      </c>
-      <c r="M38" s="8" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N38" s="8" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
@@ -2738,57 +3357,18 @@
       <c r="BV38" s="3"/>
     </row>
     <row r="39" spans="2:74" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="8" t="e">
-        <f t="shared" ref="C39:H39" si="26">+C24/C23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D39" s="8" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E39" s="8">
-        <f t="shared" si="26"/>
-        <v>1.3736263736263736E-2</v>
-      </c>
-      <c r="F39" s="8" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G39" s="8">
-        <f t="shared" si="26"/>
-        <v>-6.640625E-2</v>
-      </c>
-      <c r="H39" s="8">
-        <f t="shared" si="26"/>
-        <v>0.15763546798029557</v>
-      </c>
-      <c r="I39" s="8">
-        <f>+I24/I23</f>
-        <v>3.7209302325581395E-2</v>
-      </c>
-      <c r="J39" s="8" t="e">
-        <f t="shared" ref="J39:N39" si="27">+J24/J23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K39" s="8">
-        <f t="shared" si="27"/>
-        <v>0.11428571428571428</v>
-      </c>
-      <c r="L39" s="8">
-        <f t="shared" si="27"/>
-        <v>0.1603336422613531</v>
-      </c>
-      <c r="M39" s="8" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N39" s="8" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
@@ -18538,154 +19118,6 @@
       <c r="BU251" s="3"/>
       <c r="BV251" s="3"/>
     </row>
-    <row r="252" spans="3:74" x14ac:dyDescent="0.2">
-      <c r="C252" s="3"/>
-      <c r="D252" s="3"/>
-      <c r="E252" s="3"/>
-      <c r="F252" s="3"/>
-      <c r="G252" s="3"/>
-      <c r="H252" s="3"/>
-      <c r="I252" s="3"/>
-      <c r="J252" s="3"/>
-      <c r="K252" s="3"/>
-      <c r="L252" s="3"/>
-      <c r="M252" s="3"/>
-      <c r="N252" s="3"/>
-      <c r="O252" s="3"/>
-      <c r="P252" s="3"/>
-      <c r="Q252" s="3"/>
-      <c r="R252" s="3"/>
-      <c r="S252" s="3"/>
-      <c r="T252" s="3"/>
-      <c r="U252" s="3"/>
-      <c r="V252" s="3"/>
-      <c r="W252" s="3"/>
-      <c r="X252" s="3"/>
-      <c r="Y252" s="3"/>
-      <c r="Z252" s="3"/>
-      <c r="AA252" s="3"/>
-      <c r="AB252" s="3"/>
-      <c r="AC252" s="3"/>
-      <c r="AD252" s="3"/>
-      <c r="AE252" s="3"/>
-      <c r="AF252" s="3"/>
-      <c r="AG252" s="3"/>
-      <c r="AH252" s="3"/>
-      <c r="AI252" s="3"/>
-      <c r="AJ252" s="3"/>
-      <c r="AK252" s="3"/>
-      <c r="AL252" s="3"/>
-      <c r="AM252" s="3"/>
-      <c r="AN252" s="3"/>
-      <c r="AO252" s="3"/>
-      <c r="AP252" s="3"/>
-      <c r="AQ252" s="3"/>
-      <c r="AR252" s="3"/>
-      <c r="AS252" s="3"/>
-      <c r="AT252" s="3"/>
-      <c r="AU252" s="3"/>
-      <c r="AV252" s="3"/>
-      <c r="AW252" s="3"/>
-      <c r="AX252" s="3"/>
-      <c r="AY252" s="3"/>
-      <c r="AZ252" s="3"/>
-      <c r="BA252" s="3"/>
-      <c r="BB252" s="3"/>
-      <c r="BC252" s="3"/>
-      <c r="BD252" s="3"/>
-      <c r="BE252" s="3"/>
-      <c r="BF252" s="3"/>
-      <c r="BG252" s="3"/>
-      <c r="BH252" s="3"/>
-      <c r="BI252" s="3"/>
-      <c r="BJ252" s="3"/>
-      <c r="BK252" s="3"/>
-      <c r="BL252" s="3"/>
-      <c r="BM252" s="3"/>
-      <c r="BN252" s="3"/>
-      <c r="BO252" s="3"/>
-      <c r="BP252" s="3"/>
-      <c r="BQ252" s="3"/>
-      <c r="BR252" s="3"/>
-      <c r="BS252" s="3"/>
-      <c r="BT252" s="3"/>
-      <c r="BU252" s="3"/>
-      <c r="BV252" s="3"/>
-    </row>
-    <row r="253" spans="3:74" x14ac:dyDescent="0.2">
-      <c r="C253" s="3"/>
-      <c r="D253" s="3"/>
-      <c r="E253" s="3"/>
-      <c r="F253" s="3"/>
-      <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
-      <c r="I253" s="3"/>
-      <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
-      <c r="L253" s="3"/>
-      <c r="M253" s="3"/>
-      <c r="N253" s="3"/>
-      <c r="O253" s="3"/>
-      <c r="P253" s="3"/>
-      <c r="Q253" s="3"/>
-      <c r="R253" s="3"/>
-      <c r="S253" s="3"/>
-      <c r="T253" s="3"/>
-      <c r="U253" s="3"/>
-      <c r="V253" s="3"/>
-      <c r="W253" s="3"/>
-      <c r="X253" s="3"/>
-      <c r="Y253" s="3"/>
-      <c r="Z253" s="3"/>
-      <c r="AA253" s="3"/>
-      <c r="AB253" s="3"/>
-      <c r="AC253" s="3"/>
-      <c r="AD253" s="3"/>
-      <c r="AE253" s="3"/>
-      <c r="AF253" s="3"/>
-      <c r="AG253" s="3"/>
-      <c r="AH253" s="3"/>
-      <c r="AI253" s="3"/>
-      <c r="AJ253" s="3"/>
-      <c r="AK253" s="3"/>
-      <c r="AL253" s="3"/>
-      <c r="AM253" s="3"/>
-      <c r="AN253" s="3"/>
-      <c r="AO253" s="3"/>
-      <c r="AP253" s="3"/>
-      <c r="AQ253" s="3"/>
-      <c r="AR253" s="3"/>
-      <c r="AS253" s="3"/>
-      <c r="AT253" s="3"/>
-      <c r="AU253" s="3"/>
-      <c r="AV253" s="3"/>
-      <c r="AW253" s="3"/>
-      <c r="AX253" s="3"/>
-      <c r="AY253" s="3"/>
-      <c r="AZ253" s="3"/>
-      <c r="BA253" s="3"/>
-      <c r="BB253" s="3"/>
-      <c r="BC253" s="3"/>
-      <c r="BD253" s="3"/>
-      <c r="BE253" s="3"/>
-      <c r="BF253" s="3"/>
-      <c r="BG253" s="3"/>
-      <c r="BH253" s="3"/>
-      <c r="BI253" s="3"/>
-      <c r="BJ253" s="3"/>
-      <c r="BK253" s="3"/>
-      <c r="BL253" s="3"/>
-      <c r="BM253" s="3"/>
-      <c r="BN253" s="3"/>
-      <c r="BO253" s="3"/>
-      <c r="BP253" s="3"/>
-      <c r="BQ253" s="3"/>
-      <c r="BR253" s="3"/>
-      <c r="BS253" s="3"/>
-      <c r="BT253" s="3"/>
-      <c r="BU253" s="3"/>
-      <c r="BV253" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{F8304804-F3E3-4EDA-A615-DDBE6EF75813}"/>
